--- a/CSDL.xlsx
+++ b/CSDL.xlsx
@@ -39,7 +39,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'DSTN-TT'!$A$1:$M$59</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Công nhận tốt nghiệp'!$7:$7</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
@@ -30328,9 +30328,9 @@
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="AV2:AV3"/>
+    <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="P2:P3"/>
